--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486436_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486436_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.0138</v>
+        <v>8.057499999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>5.0172</v>
+        <v>4.9992</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9966</v>
+        <v>3.0583</v>
       </c>
       <c r="G2" t="n">
         <v>2.8907</v>
@@ -610,13 +610,13 @@
         <v>1.305</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8186</v>
+        <v>0.8622</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2091</v>
+        <v>0.1911</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6095</v>
+        <v>0.6711</v>
       </c>
       <c r="V2" t="n">
         <v>2.9995</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.6229</v>
+        <v>6.6702</v>
       </c>
       <c r="E3" t="n">
-        <v>4.4725</v>
+        <v>5.2116</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1504</v>
+        <v>1.4586</v>
       </c>
       <c r="G3" t="n">
         <v>4.5664</v>
@@ -688,13 +688,13 @@
         <v>2.1751</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.596</v>
+        <v>0.4512</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9469</v>
+        <v>-0.2079</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3509</v>
+        <v>0.6591</v>
       </c>
       <c r="V3" t="n">
         <v>0.5649999999999999</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.4363</v>
+        <v>4.1001</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0897</v>
+        <v>2.5994</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3465</v>
+        <v>1.5007</v>
       </c>
       <c r="G4" t="n">
         <v>4.1143</v>
@@ -766,13 +766,13 @@
         <v>2.1751</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2143</v>
+        <v>0.8781</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7367</v>
+        <v>0.2464</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4777</v>
+        <v>0.6318</v>
       </c>
       <c r="V4" t="n">
         <v>0.1952</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. MUÑOZ BORCHERS</t>
+          <t>T. BORG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,40 +799,40 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.8977</v>
+        <v>3.1388</v>
       </c>
       <c r="E5" t="n">
-        <v>3.1908</v>
+        <v>1.903</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7068</v>
+        <v>1.2358</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1964</v>
+        <v>1.3602</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6659</v>
+        <v>1.2256</v>
       </c>
       <c r="I5" t="n">
-        <v>1.8623</v>
+        <v>0.1347</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1201</v>
+        <v>1.8369</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.845</v>
+        <v>0.8974</v>
       </c>
       <c r="L5" t="n">
-        <v>2.9651</v>
+        <v>0.9395</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9237</v>
+        <v>-0.4767</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1792</v>
+        <v>0.3282</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.1029</v>
+        <v>-0.8048999999999999</v>
       </c>
       <c r="P5" t="n">
         <v>1.7401</v>
@@ -844,28 +844,28 @@
         <v>1.7401</v>
       </c>
       <c r="S5" t="n">
-        <v>2.0912</v>
+        <v>0.2337</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0707</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>1.0205</v>
+        <v>0.1676</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.13</v>
+        <v>-0.1952</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.13</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V. VUCETIC</t>
+          <t>A. MUÑOZ BORCHERS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.5719</v>
+        <v>2.6957</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4233</v>
+        <v>2.2355</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1487</v>
+        <v>0.4603</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9519</v>
+        <v>1.1964</v>
       </c>
       <c r="H6" t="n">
-        <v>1.7791</v>
+        <v>-0.6659</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8272</v>
+        <v>1.8623</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1767</v>
+        <v>2.1201</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9855</v>
+        <v>-0.845</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1912</v>
+        <v>2.9651</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2248</v>
+        <v>-0.9237</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7936</v>
+        <v>0.1792</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.0184</v>
+        <v>-1.1029</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.7401</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.0875</v>
+        <v>1.7401</v>
       </c>
       <c r="S6" t="n">
-        <v>1.62</v>
+        <v>0.8893</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3341</v>
+        <v>0.1154</v>
       </c>
       <c r="U6" t="n">
-        <v>1.2859</v>
+        <v>0.7739</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. BORG</t>
+          <t>X. OROZ URIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.9545</v>
+        <v>1.9046</v>
       </c>
       <c r="E7" t="n">
-        <v>1.027</v>
+        <v>0.8887</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9276</v>
+        <v>1.0159</v>
       </c>
       <c r="G7" t="n">
-        <v>1.3602</v>
+        <v>1.3829</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2256</v>
+        <v>0.9215</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1347</v>
+        <v>0.4614</v>
       </c>
       <c r="J7" t="n">
-        <v>1.8369</v>
+        <v>0.9271</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8974</v>
+        <v>0.2769</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9395</v>
+        <v>0.6502</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4767</v>
+        <v>0.4557</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3282</v>
+        <v>0.6446</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8048999999999999</v>
+        <v>-0.1889</v>
       </c>
       <c r="P7" t="n">
-        <v>1.7401</v>
+        <v>0.87</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7401</v>
+        <v>0.87</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9505</v>
+        <v>0.7817</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8099</v>
+        <v>-0.0384</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1406</v>
+        <v>0.8201000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1952</v>
+        <v>-1.13</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1952</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X. OROZ URIA</t>
+          <t>V. VUCETIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.7839</v>
+        <v>1.8313</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4597</v>
+        <v>0.2682</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3242</v>
+        <v>1.563</v>
       </c>
       <c r="G8" t="n">
-        <v>1.3829</v>
+        <v>0.9519</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9215</v>
+        <v>1.7791</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4614</v>
+        <v>-0.8272</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9271</v>
+        <v>1.1767</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2769</v>
+        <v>0.9855</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6502</v>
+        <v>0.1912</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4557</v>
+        <v>-0.2248</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6446</v>
+        <v>0.7936</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1889</v>
+        <v>-1.0184</v>
       </c>
       <c r="P8" t="n">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R8" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6609</v>
+        <v>0.8793</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4675</v>
+        <v>0.1791</v>
       </c>
       <c r="U8" t="n">
-        <v>1.1284</v>
+        <v>0.7003</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3581</v>
+        <v>0.5906</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3731</v>
+        <v>-0.8323</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7312</v>
+        <v>1.423</v>
       </c>
       <c r="G9" t="n">
         <v>-0.3954</v>
@@ -1156,13 +1156,13 @@
         <v>1.7401</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1009</v>
+        <v>0.3335</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0274</v>
+        <v>-0.4867</v>
       </c>
       <c r="U9" t="n">
-        <v>1.1284</v>
+        <v>0.8201000000000001</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6746</v>
+        <v>-0.4704</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2183</v>
+        <v>-1.1066</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5437</v>
+        <v>0.6362</v>
       </c>
       <c r="G10" t="n">
         <v>0.4197</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0068</v>
+        <v>0.1974</v>
       </c>
       <c r="T10" t="n">
-        <v>0.012</v>
+        <v>0.1238</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0189</v>
+        <v>0.0736</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.0682</v>
+        <v>-0.8147</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0638</v>
+        <v>-1.9953</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9957</v>
+        <v>1.1806</v>
       </c>
       <c r="G11" t="n">
         <v>-0.8522</v>
@@ -1312,13 +1312,13 @@
         <v>0.87</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3682</v>
+        <v>-0.1148</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3425</v>
+        <v>-0.274</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0257</v>
+        <v>0.1592</v>
       </c>
       <c r="V11" t="n">
         <v>0.3698</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.0297</v>
+        <v>-1.9989</v>
       </c>
       <c r="E12" t="n">
         <v>-1.0693</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9604</v>
+        <v>-0.9296</v>
       </c>
       <c r="G12" t="n">
         <v>0.1673</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0205</v>
+        <v>0.0514</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0205</v>
+        <v>0.0514</v>
       </c>
       <c r="V12" t="n">
         <v>-1.13</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.3879</v>
+        <v>-6.8561</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.4751</v>
+        <v>-4.2516</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.9128</v>
+        <v>-2.6045</v>
       </c>
       <c r="G13" t="n">
         <v>-2.7849</v>
@@ -1468,13 +1468,13 @@
         <v>0.435</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7775</v>
+        <v>-0.2457</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.4614</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0925</v>
+        <v>0.2157</v>
       </c>
       <c r="V13" t="n">
         <v>-2.0854</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>17.4787</v>
+        <v>18.8487</v>
       </c>
       <c r="E14" t="n">
-        <v>7.480599999999998</v>
+        <v>8.850499999999998</v>
       </c>
       <c r="F14" t="n">
-        <v>9.998200000000001</v>
+        <v>9.998299999999999</v>
       </c>
       <c r="G14" t="n">
         <v>13.0173</v>
@@ -1528,7 +1528,7 @@
         <v>5.7135</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.9973</v>
+        <v>-3.997300000000001</v>
       </c>
       <c r="N14" t="n">
         <v>1.7162</v>
@@ -1546,13 +1546,13 @@
         <v>14.138</v>
       </c>
       <c r="S14" t="n">
-        <v>3.827400000000001</v>
+        <v>5.197299999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.9166</v>
+        <v>-0.5465</v>
       </c>
       <c r="U14" t="n">
-        <v>5.7441</v>
+        <v>5.7439</v>
       </c>
       <c r="V14" t="n">
         <v>-1.5411</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.4247</v>
+        <v>7.4099</v>
       </c>
       <c r="E15" t="n">
-        <v>6.5634</v>
+        <v>7.1222</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1387</v>
+        <v>0.2877</v>
       </c>
       <c r="G15" t="n">
         <v>3.9166</v>
@@ -1624,13 +1624,13 @@
         <v>2.1751</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.5996</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.5069</v>
+        <v>-0.9481000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0927</v>
+        <v>0.3338</v>
       </c>
       <c r="V15" t="n">
         <v>3.0202</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.8015</v>
+        <v>2.8747</v>
       </c>
       <c r="E16" t="n">
-        <v>2.8924</v>
+        <v>2.7806</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.09089999999999999</v>
+        <v>0.094</v>
       </c>
       <c r="G16" t="n">
         <v>0.5051</v>
@@ -1702,13 +1702,13 @@
         <v>1.305</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1387</v>
+        <v>-0.0655</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2139</v>
+        <v>-0.3256</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0752</v>
+        <v>0.2602</v>
       </c>
       <c r="V16" t="n">
         <v>1.13</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.6807</v>
+        <v>1.0064</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9634</v>
+        <v>1.6281</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2827</v>
+        <v>-0.6217</v>
       </c>
       <c r="G17" t="n">
         <v>0.2783</v>
@@ -1780,13 +1780,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8375</v>
+        <v>0.1631</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0769</v>
+        <v>-0.4122</v>
       </c>
       <c r="U17" t="n">
-        <v>0.9144</v>
+        <v>0.5753</v>
       </c>
       <c r="V17" t="n">
         <v>0.5649999999999999</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. IZAW BOLAVIE</t>
+          <t>N. CAMACHO DE SÁ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.8158</v>
+        <v>-1.8541</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.8331</v>
+        <v>-3.5361</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0174</v>
+        <v>1.682</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.6638</v>
+        <v>-1.4654</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.8072</v>
+        <v>0.3587</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1434</v>
+        <v>-1.824</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.2922</v>
+        <v>-0.6435999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.5599</v>
+        <v>0.6935</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2677</v>
+        <v>-1.3371</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.3716</v>
+        <v>-0.8217</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.2473</v>
+        <v>-0.3348</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1243</v>
+        <v>-0.4869</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2175</v>
+        <v>-0</v>
       </c>
       <c r="Q18" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3926</v>
+        <v>2.1751</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9796</v>
+        <v>-0.3887</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0168</v>
+        <v>-0.7174</v>
       </c>
       <c r="U18" t="n">
-        <v>0.9964</v>
+        <v>0.3287</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3491</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.3491</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>N. CAMACHO DE SÁ</t>
+          <t>J. ROBERTS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.2652</v>
+        <v>-2.6026</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.9831</v>
+        <v>0.3725</v>
       </c>
       <c r="F19" t="n">
-        <v>1.7179</v>
+        <v>-2.9751</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.4654</v>
+        <v>-0.8673999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3587</v>
+        <v>-0.5414</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.824</v>
+        <v>-0.3259</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6435999999999999</v>
+        <v>0.697</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6935</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.3371</v>
+        <v>0.0765</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8217</v>
+        <v>-1.5643</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3348</v>
+        <v>-1.1619</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4869</v>
+        <v>-0.4024</v>
       </c>
       <c r="P19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1751</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7999000000000001</v>
+        <v>-0.0403</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.1644</v>
+        <v>-0.3245</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3646</v>
+        <v>0.2842</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.695</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. ROBERTS</t>
+          <t>A. IZAW BOLAVIE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.5179</v>
+        <v>-3.0039</v>
       </c>
       <c r="E20" t="n">
-        <v>0.149</v>
+        <v>-4.6154</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.6669</v>
+        <v>1.6116</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.8673999999999999</v>
+        <v>-2.6638</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5414</v>
+        <v>-2.8072</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3259</v>
+        <v>0.1434</v>
       </c>
       <c r="J20" t="n">
-        <v>0.697</v>
+        <v>-1.2922</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6205000000000001</v>
+        <v>-1.5599</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0765</v>
+        <v>0.2677</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.5643</v>
+        <v>-1.3716</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1619</v>
+        <v>-1.2473</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4024</v>
+        <v>-0.1243</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.2175</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.3926</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0445</v>
+        <v>-0.2085</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.548</v>
+        <v>-0.7991</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5924</v>
+        <v>0.5906</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.695</v>
+        <v>-0.3491</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.3491</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.695</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.7389</v>
+        <v>-3.9201</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0541</v>
+        <v>-2.3893</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6848</v>
+        <v>-1.5307</v>
       </c>
       <c r="G21" t="n">
         <v>-3.775</v>
@@ -2092,13 +2092,13 @@
         <v>0.435</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2037</v>
+        <v>-0.3848</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.3437</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1953</v>
+        <v>-0.0412</v>
       </c>
       <c r="V21" t="n">
         <v>-0.1952</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.5058</v>
+        <v>-4.4018</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4004</v>
+        <v>-2.5122</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.1054</v>
+        <v>-1.8896</v>
       </c>
       <c r="G22" t="n">
         <v>-1.2176</v>
@@ -2170,13 +2170,13 @@
         <v>0.435</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4606</v>
+        <v>-0.3566</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4194</v>
+        <v>-0.5311</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0412</v>
+        <v>0.1745</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>G. DIKE EGUN</t>
+          <t>D. SANADZE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.5955</v>
+        <v>-6.1039</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.8323</v>
+        <v>-5.0162</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.7632</v>
+        <v>-1.0877</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.6263</v>
+        <v>-4.1019</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.0804</v>
+        <v>-2.5759</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.5459</v>
+        <v>-1.526</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.2276</v>
+        <v>-2.1661</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6356000000000001</v>
+        <v>-1.9765</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5921</v>
+        <v>-0.1896</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.3987</v>
+        <v>-1.9357</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.4449</v>
+        <v>-0.5994</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.9539</v>
+        <v>-1.3364</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.0875</v>
+        <v>-1.305</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.1751</v>
+        <v>-3.2626</v>
       </c>
       <c r="R23" t="n">
-        <v>1.0875</v>
+        <v>1.9576</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9469</v>
+        <v>-0.697</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6249</v>
+        <v>-0.7174</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3221</v>
+        <v>0.0204</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.9347</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1952</v>
+        <v>1.13</v>
       </c>
       <c r="X23" t="n">
         <v>-1.13</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>D. SANADZE</t>
+          <t>G. DIKE EGUN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.9465</v>
+        <v>-6.1383</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.4632</v>
+        <v>-3.8323</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.4833</v>
+        <v>-2.306</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.1019</v>
+        <v>-3.6263</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.5759</v>
+        <v>-2.0804</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.526</v>
+        <v>-1.5459</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.1661</v>
+        <v>-1.2276</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.9765</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.1896</v>
+        <v>-0.5921</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.9357</v>
+        <v>-2.3987</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.5994</v>
+        <v>-1.4449</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.3364</v>
+        <v>-0.9539</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.305</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.2626</v>
+        <v>-2.1751</v>
       </c>
       <c r="R24" t="n">
-        <v>1.9576</v>
+        <v>1.0875</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.5396</v>
+        <v>-0.4897</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.1644</v>
+        <v>-0.6249</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3752</v>
+        <v>0.1352</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-0.9347</v>
       </c>
       <c r="W24" t="n">
-        <v>1.13</v>
+        <v>0.1952</v>
       </c>
       <c r="X24" t="n">
         <v>-1.13</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-17.4787</v>
+        <v>-16.7337</v>
       </c>
       <c r="E25" t="n">
-        <v>-9.997999999999998</v>
+        <v>-9.998100000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-7.480600000000001</v>
+        <v>-6.735500000000001</v>
       </c>
       <c r="G25" t="n">
         <v>-13.0174</v>
@@ -2374,7 +2374,7 @@
         <v>-13.0173</v>
       </c>
       <c r="I25" t="n">
-        <v>-6.661338147750939e-16</v>
+        <v>-2.220446049250313e-16</v>
       </c>
       <c r="J25" t="n">
         <v>3.997499999999999</v>
@@ -2404,13 +2404,13 @@
         <v>11.9629</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.8274</v>
+        <v>-3.0824</v>
       </c>
       <c r="T25" t="n">
         <v>-5.744</v>
       </c>
       <c r="U25" t="n">
-        <v>1.916500000000001</v>
+        <v>2.6617</v>
       </c>
       <c r="V25" t="n">
         <v>1.541199999999999</v>
